--- a/fluxogramas/fluxogramas-formas.xlsx
+++ b/fluxogramas/fluxogramas-formas.xlsx
@@ -333,6 +333,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15525750" y="609600"/>
@@ -375,6 +376,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="27527250" y="609600"/>
@@ -417,6 +419,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="39528750" y="609600"/>
@@ -459,6 +462,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="609600"/>
@@ -501,6 +505,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -536,6 +541,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -578,6 +584,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -613,6 +620,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -655,6 +663,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="895350"/>
@@ -690,6 +699,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="2038350"/>
@@ -725,6 +735,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="2038350"/>
@@ -767,6 +778,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="2038350"/>
@@ -802,6 +814,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="4324350"/>
@@ -837,6 +850,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="4324350"/>
@@ -879,6 +893,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="4324350"/>
@@ -914,6 +929,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="5467350"/>
@@ -949,6 +965,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="5467350"/>
@@ -991,6 +1008,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="5467350"/>
@@ -1026,6 +1044,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="6610350"/>
@@ -1061,6 +1080,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="6610350"/>
@@ -1103,6 +1123,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="6610350"/>
@@ -1138,6 +1159,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2276475" y="1104900"/>
@@ -1173,6 +1195,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1638300" y="1638300"/>
@@ -1207,6 +1230,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="3676650" y="1181100"/>
@@ -1251,6 +1275,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="5676900" y="2324100"/>
@@ -1295,6 +1320,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="7677150" y="2324100"/>
@@ -1339,6 +1365,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="10239375" y="2228850"/>
@@ -1381,6 +1408,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9639300" y="2838450"/>
@@ -1415,6 +1443,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11677650" y="1181100"/>
@@ -1459,6 +1488,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13677900" y="2324100"/>
@@ -1503,6 +1533,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15678150" y="2324100"/>
@@ -1547,6 +1578,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17678400" y="2324100"/>
@@ -1591,6 +1623,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="20240625" y="2228850"/>
@@ -1633,6 +1666,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19640550" y="2838450"/>
@@ -1667,6 +1701,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19678650" y="3467100"/>
@@ -1711,6 +1746,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21678900" y="1181100"/>
@@ -1755,6 +1791,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="23679150" y="2324100"/>
@@ -1799,6 +1836,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="26241375" y="2228850"/>
@@ -1841,6 +1879,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="25641300" y="2838450"/>
@@ -1875,6 +1914,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="27679650" y="2324100"/>
@@ -1919,6 +1959,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="29679900" y="2324100"/>
@@ -1963,6 +2004,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="31680150" y="1181100"/>
@@ -2007,6 +2049,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="33680400" y="6896100"/>
@@ -2051,6 +2094,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="27679650" y="4610100"/>
@@ -2095,6 +2139,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="29679900" y="4610100"/>
@@ -2139,6 +2184,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="31680150" y="4610100"/>
@@ -2183,6 +2229,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="33680400" y="4610100"/>
@@ -2227,6 +2274,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="35680650" y="4610100"/>
@@ -2271,6 +2319,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="37680900" y="4610100"/>
@@ -2315,6 +2364,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="39681150" y="2324100"/>
@@ -2359,6 +2409,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="41681400" y="1181100"/>
@@ -2403,6 +2454,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="43681650" y="5753100"/>
@@ -2447,6 +2499,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="45681900" y="6896100"/>
@@ -2491,6 +2544,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="47682150" y="6896100"/>
@@ -2535,6 +2589,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="50282475" y="6819900"/>
@@ -2570,6 +2625,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="49644300" y="7353300"/>
@@ -2604,6 +2660,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2771775" y="1352550"/>
@@ -2768,6 +2825,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13373100" y="1466850"/>
@@ -2854,6 +2912,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15373350" y="2609850"/>
@@ -2992,6 +3051,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21374100" y="1466850"/>
@@ -3104,6 +3164,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="25374600" y="2514600"/>
@@ -3190,6 +3251,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="29375100" y="2609850"/>
@@ -3354,6 +3416,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="29375100" y="4895850"/>
@@ -3687,6 +3750,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="7524750" y="609600"/>
@@ -3729,6 +3793,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15525750" y="609600"/>
@@ -3771,6 +3836,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="23526750" y="609600"/>
@@ -3813,6 +3879,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="609600"/>
@@ -3855,6 +3922,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -3890,6 +3958,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -3932,6 +4001,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -3967,6 +4037,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -4009,6 +4080,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="895350"/>
@@ -4044,6 +4116,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="2038350"/>
@@ -4079,6 +4152,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="2038350"/>
@@ -4121,6 +4195,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="2038350"/>
@@ -4156,6 +4231,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="4324350"/>
@@ -4191,6 +4267,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="4324350"/>
@@ -4233,6 +4310,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="4324350"/>
@@ -4268,6 +4346,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="6610350"/>
@@ -4303,6 +4382,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="6610350"/>
@@ -4345,6 +4425,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="6610350"/>
@@ -4380,6 +4461,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="7753350"/>
@@ -4415,6 +4497,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="7753350"/>
@@ -4457,6 +4540,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="7753350"/>
@@ -4492,6 +4576,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2276475" y="2247900"/>
@@ -4527,6 +4612,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1638300" y="2781300"/>
@@ -4561,6 +4647,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="3676650" y="2324100"/>
@@ -4605,6 +4692,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="6238875" y="2228850"/>
@@ -4647,6 +4735,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="5638800" y="2838450"/>
@@ -4681,6 +4770,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="7677150" y="2324100"/>
@@ -4725,6 +4815,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9677400" y="6896100"/>
@@ -4769,6 +4860,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11677650" y="1181100"/>
@@ -4813,6 +4905,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13677900" y="6896100"/>
@@ -4857,6 +4950,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="16240125" y="6800850"/>
@@ -4899,6 +4993,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15640050" y="7410450"/>
@@ -4933,6 +5028,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17678400" y="6896100"/>
@@ -4977,6 +5073,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19678650" y="6896100"/>
@@ -5021,6 +5118,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21678900" y="6896100"/>
@@ -5065,6 +5163,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="7677150" y="4610100"/>
@@ -5109,6 +5208,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9677400" y="4610100"/>
@@ -5153,6 +5253,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11677650" y="4610100"/>
@@ -5197,6 +5298,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="14239875" y="4514850"/>
@@ -5239,6 +5341,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13639800" y="5124450"/>
@@ -5273,6 +5376,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15678150" y="4610100"/>
@@ -5317,6 +5421,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15678150" y="5753100"/>
@@ -5361,6 +5466,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="7677150" y="3467100"/>
@@ -5405,6 +5511,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9677400" y="3467100"/>
@@ -5449,6 +5556,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11677650" y="3467100"/>
@@ -5493,6 +5601,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13677900" y="3467100"/>
@@ -5537,6 +5646,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="16240125" y="3371850"/>
@@ -5579,6 +5689,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15640050" y="3981450"/>
@@ -5613,6 +5724,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17678400" y="3467100"/>
@@ -5657,6 +5769,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="24241125" y="2228850"/>
@@ -5699,6 +5812,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="23641050" y="2838450"/>
@@ -5733,6 +5847,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="25679400" y="2324100"/>
@@ -5777,6 +5892,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="27679650" y="8039100"/>
@@ -5821,6 +5937,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="30279975" y="2247900"/>
@@ -5856,6 +5973,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="29641800" y="2781300"/>
@@ -5890,6 +6008,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2771775" y="2495550"/>
@@ -6002,6 +6121,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9372600" y="2609850"/>
@@ -6166,6 +6286,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19373850" y="7181850"/>
@@ -6278,6 +6399,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="23374350" y="2514600"/>
@@ -6364,6 +6486,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9372600" y="4895850"/>
@@ -6502,6 +6625,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17373600" y="2514600"/>
@@ -6588,6 +6712,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17373600" y="6038850"/>
@@ -6674,6 +6799,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9372600" y="3752850"/>
@@ -6838,6 +6964,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19373850" y="2514600"/>
@@ -6924,6 +7051,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="24812625" y="2514600"/>
@@ -7049,6 +7177,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="7524750" y="609600"/>
@@ -7091,6 +7220,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17526000" y="609600"/>
@@ -7133,6 +7263,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="27527250" y="609600"/>
@@ -7175,6 +7306,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="35528250" y="609600"/>
@@ -7217,6 +7349,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="43529250" y="609600"/>
@@ -7259,6 +7392,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="55530750" y="609600"/>
@@ -7301,6 +7435,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="61531500" y="609600"/>
@@ -7343,6 +7478,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="609600"/>
@@ -7385,6 +7521,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -7420,6 +7557,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -7462,6 +7600,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -7497,6 +7636,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -7539,6 +7679,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="895350"/>
@@ -7574,6 +7715,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="3181350"/>
@@ -7609,6 +7751,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="3181350"/>
@@ -7651,6 +7794,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="3181350"/>
@@ -7686,6 +7830,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="4324350"/>
@@ -7721,6 +7866,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="4324350"/>
@@ -7763,6 +7909,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="4324350"/>
@@ -7798,6 +7945,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="5467350"/>
@@ -7833,6 +7981,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="5467350"/>
@@ -7875,6 +8024,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="5467350"/>
@@ -7910,6 +8060,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="6610350"/>
@@ -7945,6 +8096,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="6610350"/>
@@ -7987,6 +8139,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="6610350"/>
@@ -8022,6 +8175,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="7753350"/>
@@ -8057,6 +8211,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="7753350"/>
@@ -8099,6 +8254,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="7753350"/>
@@ -8134,6 +8290,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="8896350"/>
@@ -8169,6 +8326,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="8896350"/>
@@ -8211,6 +8369,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="8896350"/>
@@ -8246,6 +8405,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="11182350"/>
@@ -8281,6 +8441,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="11182350"/>
@@ -8323,6 +8484,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="11182350"/>
@@ -8358,6 +8520,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2276475" y="1104900"/>
@@ -8393,6 +8556,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1638300" y="1638300"/>
@@ -8427,6 +8591,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="3676650" y="3467100"/>
@@ -8471,6 +8636,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="5676900" y="3467100"/>
@@ -8515,6 +8681,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="7677150" y="1181100"/>
@@ -8559,6 +8726,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="10239375" y="1085850"/>
@@ -8601,6 +8769,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9639300" y="1695450"/>
@@ -8635,6 +8804,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11677650" y="1181100"/>
@@ -8679,6 +8849,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11677650" y="2324100"/>
@@ -8723,6 +8894,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13677900" y="3467100"/>
@@ -8767,6 +8939,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="16240125" y="3371850"/>
@@ -8809,6 +8982,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15640050" y="3981450"/>
@@ -8843,6 +9017,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="18278475" y="1104900"/>
@@ -8878,6 +9053,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17640300" y="1638300"/>
@@ -8912,6 +9088,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17678400" y="4610100"/>
@@ -8956,6 +9133,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19678650" y="4610100"/>
@@ -9000,6 +9178,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="22240875" y="4514850"/>
@@ -9042,6 +9221,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21640800" y="5124450"/>
@@ -9076,6 +9256,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="24241125" y="4514850"/>
@@ -9118,6 +9299,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="23641050" y="5124450"/>
@@ -9152,6 +9334,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="25679400" y="9182100"/>
@@ -9196,6 +9379,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="26279475" y="1104900"/>
@@ -9231,6 +9415,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="25641300" y="1638300"/>
@@ -9265,6 +9450,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="27679650" y="3467100"/>
@@ -9309,6 +9495,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="29679900" y="3467100"/>
@@ -9353,6 +9540,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="32242125" y="3371850"/>
@@ -9395,6 +9583,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="31642050" y="3981450"/>
@@ -9429,6 +9618,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="33680400" y="5753100"/>
@@ -9473,6 +9663,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="27679650" y="10325100"/>
@@ -9517,6 +9708,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="29679900" y="1181100"/>
@@ -9561,6 +9753,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="32280225" y="10248900"/>
@@ -9596,6 +9789,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="31642050" y="10782300"/>
@@ -9630,6 +9824,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="35680650" y="3467100"/>
@@ -9674,6 +9869,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="38242875" y="3371850"/>
@@ -9716,6 +9912,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="37642800" y="3981450"/>
@@ -9750,6 +9947,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="39681150" y="8039100"/>
@@ -9794,6 +9992,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="41681400" y="1181100"/>
@@ -9838,6 +10037,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="43681650" y="11468100"/>
@@ -9882,6 +10082,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="46243875" y="3371850"/>
@@ -9924,6 +10125,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="45643800" y="3981450"/>
@@ -9958,6 +10160,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="47682150" y="6896100"/>
@@ -10002,6 +10205,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="49682400" y="3467100"/>
@@ -10046,6 +10250,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="51682650" y="6896100"/>
@@ -10090,6 +10295,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="54282975" y="1104900"/>
@@ -10125,6 +10331,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="53644800" y="1638300"/>
@@ -10159,6 +10366,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="56283225" y="1104900"/>
@@ -10194,6 +10402,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="55645050" y="1638300"/>
@@ -10228,6 +10437,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57683400" y="3467100"/>
@@ -10272,6 +10482,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="60283725" y="3390900"/>
@@ -10307,6 +10518,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="59645550" y="3924300"/>
@@ -10341,6 +10553,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="61683900" y="8039100"/>
@@ -10385,6 +10598,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="64284225" y="7962900"/>
@@ -10420,6 +10634,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="63646050" y="8496300"/>
@@ -10454,6 +10669,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2771775" y="1352550"/>
@@ -10618,6 +10834,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="10810875" y="1371600"/>
@@ -10678,6 +10895,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13373100" y="1466850"/>
@@ -10816,6 +11034,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="16811625" y="3657600"/>
@@ -10876,6 +11095,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19373850" y="4895850"/>
@@ -10988,6 +11208,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="22812375" y="4800600"/>
@@ -11048,6 +11269,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="24812625" y="4800600"/>
@@ -11108,6 +11330,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="24812625" y="4800600"/>
@@ -11168,6 +11391,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="27374850" y="9467850"/>
@@ -11306,6 +11530,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="29375100" y="3752850"/>
@@ -11418,6 +11643,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="35375850" y="3752850"/>
@@ -11504,6 +11730,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="37376100" y="3657600"/>
@@ -11590,6 +11817,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="41376600" y="1466850"/>
@@ -11676,6 +11904,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="43376850" y="1466850"/>
@@ -11788,6 +12017,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="49377600" y="3752850"/>
@@ -11874,6 +12104,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="51377850" y="3752850"/>
@@ -12051,6 +12282,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9525000" y="609600"/>
@@ -12093,6 +12325,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17526000" y="609600"/>
@@ -12135,6 +12368,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="31527750" y="609600"/>
@@ -12177,6 +12411,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="609600"/>
@@ -12219,6 +12454,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -12254,6 +12490,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -12296,6 +12533,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -12331,6 +12569,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -12373,6 +12612,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="895350"/>
@@ -12408,6 +12648,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="3181350"/>
@@ -12443,6 +12684,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="3181350"/>
@@ -12485,6 +12727,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="3181350"/>
@@ -12520,6 +12763,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="4324350"/>
@@ -12555,6 +12799,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="4324350"/>
@@ -12597,6 +12842,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="4324350"/>
@@ -12632,6 +12878,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="5467350"/>
@@ -12667,6 +12914,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="5467350"/>
@@ -12709,6 +12957,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="5467350"/>
@@ -12744,6 +12993,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="6610350"/>
@@ -12779,6 +13029,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="6610350"/>
@@ -12821,6 +13072,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="6610350"/>
@@ -12856,6 +13108,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2276475" y="3390900"/>
@@ -12891,6 +13144,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1638300" y="3924300"/>
@@ -12925,6 +13179,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="3676650" y="3467100"/>
@@ -12969,6 +13224,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="5676900" y="3467100"/>
@@ -13013,6 +13269,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="7677150" y="1181100"/>
@@ -13057,6 +13314,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="10239375" y="1085850"/>
@@ -13099,6 +13357,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9639300" y="1695450"/>
@@ -13133,6 +13392,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11677650" y="1181100"/>
@@ -13177,6 +13437,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11677650" y="2324100"/>
@@ -13221,6 +13482,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13677900" y="3467100"/>
@@ -13265,6 +13527,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="16240125" y="3371850"/>
@@ -13307,6 +13570,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15640050" y="3981450"/>
@@ -13341,6 +13605,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="18278475" y="1104900"/>
@@ -13376,6 +13641,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17640300" y="1638300"/>
@@ -13410,6 +13676,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17678400" y="3467100"/>
@@ -13454,6 +13721,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19678650" y="3467100"/>
@@ -13498,6 +13766,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21678900" y="4610100"/>
@@ -13542,6 +13811,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="24241125" y="4514850"/>
@@ -13584,6 +13854,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="23641050" y="5124450"/>
@@ -13618,6 +13889,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="25679400" y="3467100"/>
@@ -13662,6 +13934,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="27679650" y="4610100"/>
@@ -13706,6 +13979,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="30241875" y="4514850"/>
@@ -13748,6 +14022,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="29641800" y="5124450"/>
@@ -13782,6 +14057,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="31680150" y="3467100"/>
@@ -13826,6 +14102,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="34280475" y="1104900"/>
@@ -13861,6 +14138,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="33642300" y="1638300"/>
@@ -13895,6 +14173,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="31680150" y="4610100"/>
@@ -13939,6 +14218,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="33680400" y="4610100"/>
@@ -13983,6 +14263,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="35680650" y="4610100"/>
@@ -14027,6 +14308,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="37680900" y="3467100"/>
@@ -14071,6 +14353,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="39681150" y="5753100"/>
@@ -14115,6 +14398,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="41681400" y="6896100"/>
@@ -14159,6 +14443,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="44281725" y="6819900"/>
@@ -14194,6 +14479,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="43643550" y="7353300"/>
@@ -14228,6 +14514,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2771775" y="3638550"/>
@@ -14392,6 +14679,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="10810875" y="1371600"/>
@@ -14452,6 +14740,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13373100" y="1466850"/>
@@ -14590,6 +14879,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="16811625" y="3657600"/>
@@ -14650,6 +14940,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19373850" y="3752850"/>
@@ -14788,6 +15079,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="27374850" y="3752850"/>
@@ -14874,6 +15166,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="29375100" y="4800600"/>
@@ -14960,6 +15253,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="33375600" y="1352550"/>
@@ -15046,6 +15340,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="33375600" y="4895850"/>
@@ -15249,6 +15544,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11525250" y="609600"/>
@@ -15291,6 +15587,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21526500" y="609600"/>
@@ -15333,6 +15630,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="609600"/>
@@ -15375,6 +15673,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -15410,6 +15709,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -15452,6 +15752,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -15487,6 +15788,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -15529,6 +15831,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="895350"/>
@@ -15564,6 +15867,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="2038350"/>
@@ -15599,6 +15903,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="2038350"/>
@@ -15641,6 +15946,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="2038350"/>
@@ -15676,6 +15982,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="3181350"/>
@@ -15711,6 +16018,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="3181350"/>
@@ -15753,6 +16061,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="3181350"/>
@@ -15788,6 +16097,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="5467350"/>
@@ -15823,6 +16133,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="5467350"/>
@@ -15865,6 +16176,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="5467350"/>
@@ -15900,6 +16212,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2276475" y="2247900"/>
@@ -15935,6 +16248,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1638300" y="2781300"/>
@@ -15969,6 +16283,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="3676650" y="2324100"/>
@@ -16013,6 +16328,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="5676900" y="2324100"/>
@@ -16057,6 +16373,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="7677150" y="3467100"/>
@@ -16101,6 +16418,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9677400" y="3467100"/>
@@ -16145,6 +16463,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11677650" y="3467100"/>
@@ -16189,6 +16508,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="14239875" y="3371850"/>
@@ -16231,6 +16551,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13639800" y="3981450"/>
@@ -16265,6 +16586,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15678150" y="1181100"/>
@@ -16309,6 +16631,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17678400" y="3467100"/>
@@ -16353,6 +16676,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19678650" y="3467100"/>
@@ -16397,6 +16721,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21678900" y="3467100"/>
@@ -16441,6 +16766,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="24241125" y="3371850"/>
@@ -16483,6 +16809,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="23641050" y="3981450"/>
@@ -16517,6 +16844,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="25679400" y="3467100"/>
@@ -16561,6 +16889,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="27679650" y="2324100"/>
@@ -16605,6 +16934,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="30279975" y="2247900"/>
@@ -16640,6 +16970,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="29641800" y="2781300"/>
@@ -16674,6 +17005,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="25679400" y="4610100"/>
@@ -16718,6 +17050,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="27679650" y="4610100"/>
@@ -16762,6 +17095,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="29679900" y="4610100"/>
@@ -16806,6 +17140,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="31680150" y="5753100"/>
@@ -16850,6 +17185,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="34280475" y="4533900"/>
@@ -16885,6 +17221,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="33642300" y="5067300"/>
@@ -16919,6 +17256,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2771775" y="2495550"/>
@@ -17135,6 +17473,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17373600" y="1466850"/>
@@ -17221,6 +17560,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19373850" y="3752850"/>
@@ -17359,6 +17699,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="27374850" y="2609850"/>
@@ -17471,6 +17812,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="27374850" y="4895850"/>
@@ -17622,6 +17964,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11525250" y="609600"/>
@@ -17664,6 +18007,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19526250" y="609600"/>
@@ -17706,6 +18050,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="29527500" y="609600"/>
@@ -17748,6 +18093,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="609600"/>
@@ -17790,6 +18136,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -17825,6 +18172,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -17867,6 +18215,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -17902,6 +18251,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -17944,6 +18294,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="895350"/>
@@ -17979,6 +18330,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="2038350"/>
@@ -18014,6 +18366,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="2038350"/>
@@ -18056,6 +18409,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="2038350"/>
@@ -18091,6 +18445,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="3181350"/>
@@ -18126,6 +18481,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="3181350"/>
@@ -18168,6 +18524,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="3181350"/>
@@ -18203,6 +18560,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="4324350"/>
@@ -18238,6 +18596,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="4324350"/>
@@ -18280,6 +18639,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="4324350"/>
@@ -18315,6 +18675,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="5467350"/>
@@ -18350,6 +18711,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="5467350"/>
@@ -18392,6 +18754,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="5467350"/>
@@ -18427,6 +18790,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="6610350"/>
@@ -18462,6 +18826,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="6610350"/>
@@ -18504,6 +18869,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="6610350"/>
@@ -18539,6 +18905,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2276475" y="2247900"/>
@@ -18574,6 +18941,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1638300" y="2781300"/>
@@ -18608,6 +18976,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="3676650" y="3467100"/>
@@ -18652,6 +19021,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="5676900" y="3467100"/>
@@ -18696,6 +19066,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="7677150" y="3467100"/>
@@ -18740,6 +19111,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9677400" y="3467100"/>
@@ -18784,6 +19156,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="12239625" y="2228850"/>
@@ -18826,6 +19199,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11639550" y="2838450"/>
@@ -18860,6 +19234,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13677900" y="1181100"/>
@@ -18904,6 +19279,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15678150" y="1181100"/>
@@ -18948,6 +19324,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17678400" y="5753100"/>
@@ -18992,6 +19369,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="20240625" y="5657850"/>
@@ -19034,6 +19412,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19640550" y="6267450"/>
@@ -19068,6 +19447,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="22278975" y="5676900"/>
@@ -19103,6 +19483,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21640800" y="6210300"/>
@@ -19137,6 +19518,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21678900" y="4610100"/>
@@ -19181,6 +19563,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="23679150" y="6896100"/>
@@ -19225,6 +19608,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="25679400" y="2324100"/>
@@ -19269,6 +19653,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="28241625" y="2228850"/>
@@ -19311,6 +19696,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="27641550" y="2838450"/>
@@ -19345,6 +19731,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="29679900" y="4610100"/>
@@ -19389,6 +19776,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="32280225" y="4533900"/>
@@ -19424,6 +19812,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="31642050" y="5067300"/>
@@ -19458,6 +19847,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="29679900" y="2324100"/>
@@ -19502,6 +19892,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="31680150" y="3467100"/>
@@ -19546,6 +19937,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="33680400" y="3467100"/>
@@ -19590,6 +19982,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="35680650" y="3467100"/>
@@ -19634,6 +20027,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="38280975" y="3390900"/>
@@ -19669,6 +20063,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="37642800" y="3924300"/>
@@ -19703,6 +20098,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2771775" y="2495550"/>
@@ -19893,6 +20289,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="12811125" y="1466850"/>
@@ -19953,6 +20350,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15373350" y="1466850"/>
@@ -20091,6 +20489,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="20812125" y="4895850"/>
@@ -20151,6 +20550,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="23374350" y="4895850"/>
@@ -20289,6 +20689,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="31375350" y="4781550"/>
@@ -20375,6 +20776,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="31375350" y="2609850"/>
@@ -20526,6 +20928,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9525000" y="609600"/>
@@ -20568,6 +20971,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21526500" y="609600"/>
@@ -20610,6 +21014,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="29527500" y="609600"/>
@@ -20652,6 +21057,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="609600"/>
@@ -20694,6 +21100,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -20729,6 +21136,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -20771,6 +21179,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -20806,6 +21215,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -20848,6 +21258,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="895350"/>
@@ -20883,6 +21294,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="2038350"/>
@@ -20918,6 +21330,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="2038350"/>
@@ -20960,6 +21373,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="2038350"/>
@@ -20995,6 +21409,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="4324350"/>
@@ -21030,6 +21445,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="4324350"/>
@@ -21072,6 +21488,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="4324350"/>
@@ -21107,6 +21524,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="5467350"/>
@@ -21142,6 +21560,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="5467350"/>
@@ -21184,6 +21603,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="5467350"/>
@@ -21219,6 +21639,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2276475" y="1104900"/>
@@ -21254,6 +21675,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1638300" y="1638300"/>
@@ -21288,6 +21710,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="3676650" y="1181100"/>
@@ -21332,6 +21755,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="5676900" y="2324100"/>
@@ -21376,6 +21800,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="7677150" y="2324100"/>
@@ -21420,6 +21845,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9677400" y="2324100"/>
@@ -21464,6 +21890,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11677650" y="2324100"/>
@@ -21508,6 +21935,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="14239875" y="2228850"/>
@@ -21550,6 +21978,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13639800" y="2838450"/>
@@ -21584,6 +22013,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15678150" y="4610100"/>
@@ -21628,6 +22058,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17678400" y="2324100"/>
@@ -21672,6 +22103,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19678650" y="5753100"/>
@@ -21716,6 +22148,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="22240875" y="2228850"/>
@@ -21758,6 +22191,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21640800" y="2838450"/>
@@ -21792,6 +22226,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="23679150" y="2324100"/>
@@ -21836,6 +22271,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="25679400" y="1181100"/>
@@ -21880,6 +22316,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="27679650" y="2324100"/>
@@ -21924,6 +22361,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="23679150" y="3467100"/>
@@ -21968,6 +22406,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="29679900" y="2324100"/>
@@ -22012,6 +22451,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="31680150" y="2324100"/>
@@ -22056,6 +22496,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="33680400" y="2324100"/>
@@ -22100,6 +22541,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="36280725" y="2247900"/>
@@ -22135,6 +22577,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="35642550" y="2781300"/>
@@ -22169,6 +22612,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2771775" y="1352550"/>
@@ -22385,6 +22829,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17373600" y="2609850"/>
@@ -22471,6 +22916,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19373850" y="2609850"/>
@@ -22583,6 +23029,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="25374600" y="1466850"/>
@@ -22721,6 +23168,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="25374600" y="2609850"/>
@@ -22872,6 +23320,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11525250" y="609600"/>
@@ -22914,6 +23363,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15525750" y="609600"/>
@@ -22956,6 +23406,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21526500" y="609600"/>
@@ -22998,6 +23449,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="609600"/>
@@ -23040,6 +23492,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -23075,6 +23528,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -23117,6 +23571,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -23152,6 +23607,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -23194,6 +23650,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="895350"/>
@@ -23229,6 +23686,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="3181350"/>
@@ -23264,6 +23722,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="3181350"/>
@@ -23306,6 +23765,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="3181350"/>
@@ -23341,6 +23801,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="5467350"/>
@@ -23376,6 +23837,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="5467350"/>
@@ -23418,6 +23880,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="5467350"/>
@@ -23453,6 +23916,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="6610350"/>
@@ -23488,6 +23952,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="6610350"/>
@@ -23530,6 +23995,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="6610350"/>
@@ -23565,6 +24031,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="8896350"/>
@@ -23600,6 +24067,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="8896350"/>
@@ -23642,6 +24110,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="8896350"/>
@@ -23677,6 +24146,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2276475" y="1104900"/>
@@ -23712,6 +24182,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1638300" y="1638300"/>
@@ -23746,6 +24217,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="3676650" y="9182100"/>
@@ -23790,6 +24262,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="5676900" y="1181100"/>
@@ -23834,6 +24307,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="8239125" y="1085850"/>
@@ -23876,6 +24350,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="7639050" y="1695450"/>
@@ -23910,6 +24385,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="10277475" y="2247900"/>
@@ -23945,6 +24421,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9639300" y="2781300"/>
@@ -23979,6 +24456,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="10239375" y="1085850"/>
@@ -24021,6 +24499,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9639300" y="1695450"/>
@@ -24055,6 +24534,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11677650" y="1181100"/>
@@ -24099,6 +24579,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13677900" y="6896100"/>
@@ -24143,6 +24624,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15678150" y="1181100"/>
@@ -24187,6 +24669,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="18240375" y="1085850"/>
@@ -24229,6 +24712,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17640300" y="1695450"/>
@@ -24263,6 +24747,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19678650" y="6896100"/>
@@ -24307,6 +24792,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21678900" y="9182100"/>
@@ -24351,6 +24837,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="23679150" y="5753100"/>
@@ -24395,6 +24882,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="26279475" y="1104900"/>
@@ -24430,6 +24918,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="25641300" y="1638300"/>
@@ -24464,6 +24953,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11677650" y="2324100"/>
@@ -24508,6 +24998,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13677900" y="5753100"/>
@@ -24552,6 +25043,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15678150" y="3467100"/>
@@ -24596,6 +25088,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="18240375" y="3371850"/>
@@ -24638,6 +25131,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17640300" y="3981450"/>
@@ -24672,6 +25166,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19678650" y="8039100"/>
@@ -24716,6 +25211,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21678900" y="10325100"/>
@@ -24760,6 +25256,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="24279225" y="3390900"/>
@@ -24795,6 +25292,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="23641050" y="3924300"/>
@@ -24829,6 +25327,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="20278725" y="4533900"/>
@@ -24864,6 +25363,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19640550" y="5067300"/>
@@ -24898,6 +25398,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2771775" y="1352550"/>
@@ -25036,6 +25537,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="8810625" y="1371600"/>
@@ -25096,6 +25598,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="10810875" y="1371600"/>
@@ -25156,6 +25659,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13373100" y="1466850"/>
@@ -25294,6 +25798,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21374100" y="7181850"/>
@@ -25380,6 +25885,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="23374350" y="6038850"/>
@@ -25492,6 +25998,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13373100" y="2609850"/>
@@ -25630,6 +26137,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21374100" y="8324850"/>
@@ -25742,6 +26250,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
 </xdr:wsDr>
 </file>
@@ -25789,6 +26298,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9525000" y="609600"/>
@@ -25831,6 +26341,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17526000" y="609600"/>
@@ -25873,6 +26384,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21526500" y="609600"/>
@@ -25915,6 +26427,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="609600"/>
@@ -25957,6 +26470,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -25992,6 +26506,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -26034,6 +26549,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -26069,6 +26585,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -26111,6 +26628,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="895350"/>
@@ -26146,6 +26664,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="2038350"/>
@@ -26181,6 +26700,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="2038350"/>
@@ -26223,6 +26743,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="2038350"/>
@@ -26258,6 +26779,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="3181350"/>
@@ -26293,6 +26815,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="3181350"/>
@@ -26335,6 +26858,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="3181350"/>
@@ -26370,6 +26894,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="5467350"/>
@@ -26405,6 +26930,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="5467350"/>
@@ -26447,6 +26973,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="5467350"/>
@@ -26482,6 +27009,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="6610350"/>
@@ -26517,6 +27045,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="6610350"/>
@@ -26559,6 +27088,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="6610350"/>
@@ -26594,6 +27124,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2276475" y="2247900"/>
@@ -26629,6 +27160,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1638300" y="2781300"/>
@@ -26663,6 +27195,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="3676650" y="2324100"/>
@@ -26707,6 +27240,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="5676900" y="2324100"/>
@@ -26751,6 +27285,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="7677150" y="2324100"/>
@@ -26795,6 +27330,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9677400" y="2324100"/>
@@ -26839,6 +27375,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11677650" y="2324100"/>
@@ -26883,6 +27420,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13677900" y="5753100"/>
@@ -26927,6 +27465,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15678150" y="1181100"/>
@@ -26971,6 +27510,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="18240375" y="1085850"/>
@@ -27013,6 +27553,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17640300" y="1695450"/>
@@ -27047,6 +27588,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19678650" y="2324100"/>
@@ -27091,6 +27633,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="22278975" y="2247900"/>
@@ -27126,6 +27669,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21640800" y="2781300"/>
@@ -27160,6 +27704,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19678650" y="4610100"/>
@@ -27204,6 +27749,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21678900" y="6896100"/>
@@ -27248,6 +27794,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="23679150" y="6896100"/>
@@ -27292,6 +27839,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="26279475" y="6819900"/>
@@ -27327,6 +27875,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="25641300" y="7353300"/>
@@ -27361,6 +27910,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2771775" y="2495550"/>
@@ -27629,6 +28179,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21374100" y="2495550"/>
@@ -27715,6 +28266,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21374100" y="4895850"/>
@@ -27840,6 +28392,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11525250" y="609600"/>
@@ -27882,6 +28435,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19526250" y="609600"/>
@@ -27924,6 +28478,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="27527250" y="609600"/>
@@ -27966,6 +28521,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="609600"/>
@@ -28008,6 +28564,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -28043,6 +28600,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -28085,6 +28643,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -28120,6 +28679,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -28162,6 +28722,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="895350"/>
@@ -28197,6 +28758,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="3181350"/>
@@ -28232,6 +28794,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="3181350"/>
@@ -28274,6 +28837,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="3181350"/>
@@ -28309,6 +28873,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="4324350"/>
@@ -28344,6 +28909,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="4324350"/>
@@ -28386,6 +28952,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="4324350"/>
@@ -28421,6 +28988,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="5467350"/>
@@ -28456,6 +29024,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="5467350"/>
@@ -28498,6 +29067,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="5467350"/>
@@ -28533,6 +29103,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2276475" y="1104900"/>
@@ -28568,6 +29139,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1638300" y="1638300"/>
@@ -28602,6 +29174,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="3676650" y="4610100"/>
@@ -28646,6 +29219,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="5676900" y="1181100"/>
@@ -28690,6 +29264,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="8239125" y="1085850"/>
@@ -28732,6 +29307,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="7639050" y="1695450"/>
@@ -28766,6 +29342,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9677400" y="5753100"/>
@@ -28810,6 +29387,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11677650" y="1181100"/>
@@ -28854,6 +29432,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13677900" y="1181100"/>
@@ -28898,6 +29477,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="16240125" y="1085850"/>
@@ -28940,6 +29520,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15640050" y="1695450"/>
@@ -28974,6 +29555,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17678400" y="2324100"/>
@@ -29018,6 +29600,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19678650" y="4610100"/>
@@ -29062,6 +29645,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21678900" y="1181100"/>
@@ -29106,6 +29690,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="23679150" y="1181100"/>
@@ -29150,6 +29735,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="26241375" y="1085850"/>
@@ -29192,6 +29778,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="25641300" y="1695450"/>
@@ -29226,6 +29813,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="27679650" y="4610100"/>
@@ -29270,6 +29858,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="29679900" y="5753100"/>
@@ -29314,6 +29903,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="31680150" y="4610100"/>
@@ -29358,6 +29948,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="33680400" y="3467100"/>
@@ -29402,6 +29993,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="36280725" y="4533900"/>
@@ -29437,6 +30029,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="35642550" y="5067300"/>
@@ -29471,6 +30064,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2771775" y="1352550"/>
@@ -29609,6 +30203,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="7372350" y="1466850"/>
@@ -29669,6 +30264,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="8810625" y="1371600"/>
@@ -29729,6 +30325,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13373100" y="1466850"/>
@@ -29841,6 +30438,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19373850" y="2609850"/>
@@ -29927,6 +30525,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21374100" y="1466850"/>
@@ -30065,6 +30664,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="26812875" y="1371600"/>
@@ -30125,6 +30725,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="29375100" y="4895850"/>
@@ -30276,6 +30877,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="7524750" y="609600"/>
@@ -30318,6 +30920,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19526250" y="609600"/>
@@ -30360,6 +30963,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="609600"/>
@@ -30402,6 +31006,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -30437,6 +31042,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="57150" y="895350"/>
@@ -30479,6 +31085,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -30514,6 +31121,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="895350"/>
@@ -30556,6 +31164,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="895350"/>
@@ -30591,6 +31200,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="2038350"/>
@@ -30626,6 +31236,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="2038350"/>
@@ -30668,6 +31279,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="2038350"/>
@@ -30703,6 +31315,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="5467350"/>
@@ -30738,6 +31351,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="5467350"/>
@@ -30780,6 +31394,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="5467350"/>
@@ -30815,6 +31430,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="6610350"/>
@@ -30850,6 +31466,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="6610350"/>
@@ -30892,6 +31509,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="6610350"/>
@@ -30927,6 +31545,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="7753350"/>
@@ -30962,6 +31581,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="323850" y="7753350"/>
@@ -31004,6 +31624,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1524000" y="7753350"/>
@@ -31039,6 +31660,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2276475" y="2247900"/>
@@ -31074,6 +31696,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="1638300" y="2781300"/>
@@ -31108,6 +31731,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="3676650" y="2324100"/>
@@ -31152,6 +31776,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="6238875" y="2228850"/>
@@ -31194,6 +31819,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="5638800" y="2838450"/>
@@ -31228,6 +31854,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="7677150" y="2324100"/>
@@ -31272,6 +31899,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9677400" y="6896100"/>
@@ -31316,6 +31944,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11677650" y="2324100"/>
@@ -31360,6 +31989,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13677900" y="2324100"/>
@@ -31404,6 +32034,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15678150" y="5753100"/>
@@ -31448,6 +32079,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17678400" y="2324100"/>
@@ -31492,6 +32124,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19678650" y="8039100"/>
@@ -31536,6 +32169,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="22278975" y="7962900"/>
@@ -31571,6 +32205,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="21640800" y="8496300"/>
@@ -31605,6 +32240,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="7677150" y="3467100"/>
@@ -31649,6 +32285,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9677400" y="3467100"/>
@@ -31693,6 +32330,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="11677650" y="1181100"/>
@@ -31737,6 +32375,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="14239875" y="3371850"/>
@@ -31779,6 +32418,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="13639800" y="3981450"/>
@@ -31813,6 +32453,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15678150" y="3467100"/>
@@ -31857,6 +32498,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17678400" y="3467100"/>
@@ -31901,6 +32543,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="20278725" y="1104900"/>
@@ -31936,6 +32579,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="19640550" y="1638300"/>
@@ -31970,6 +32614,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="15678150" y="4610100"/>
@@ -32014,6 +32659,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="2771775" y="2495550"/>
@@ -32126,6 +32772,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9372600" y="2609850"/>
@@ -32368,6 +33015,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="9372600" y="3752850"/>
@@ -32506,6 +33154,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17373600" y="3752850"/>
@@ -32618,6 +33267,7 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
     <xdr:pos x="17373600" y="4895850"/>
